--- a/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/anova_env.xlsx
+++ b/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/anova_env.xlsx
@@ -490,38 +490,38 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>313.91</v>
+        <v>219.09</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>451.52</v>
+        <v>439.71</v>
       </c>
       <c r="F2" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G2" t="n">
-        <v>19.12</v>
+        <v>10.71</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.0000***</t>
+          <t>0.0002***</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.37 ± 0.93</t>
+          <t>7.78 ± 1.01</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2.81 ± 0.44</t>
+          <t>2.68 ± 0.57</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>3.45 ± 0.69</t>
+          <t>3.82 ± 0.85</t>
         </is>
       </c>
     </row>
@@ -535,38 +535,38 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3.45</v>
+        <v>2.62</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>21.34</v>
+        <v>18.95</v>
       </c>
       <c r="F3" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G3" t="n">
-        <v>4.45</v>
+        <v>2.98</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0162*</t>
+          <t>0.0616.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.83 ± 0.20</t>
+          <t>0.85 ± 0.20</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1.28 ± 0.09</t>
+          <t>1.34 ± 0.11</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.46 ± 0.16</t>
+          <t>1.37 ± 0.20</t>
         </is>
       </c>
     </row>
@@ -580,38 +580,38 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18.78</v>
+        <v>8.16</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>284</v>
+        <v>261.71</v>
       </c>
       <c r="F4" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G4" t="n">
-        <v>1.82</v>
+        <v>0.67</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.1719</t>
+          <t>0.5167</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>18.64 ± 0.64</t>
+          <t>18.92 ± 0.63</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>19.78 ± 0.35</t>
+          <t>19.55 ± 0.45</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>20.08 ± 0.62</t>
+          <t>19.96 ± 0.79</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LOI (%)</t>
+          <t>Water DO Bottom (mg/L)</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -631,32 +631,32 @@
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>139.51</v>
+        <v>115.55</v>
       </c>
       <c r="F5" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G5" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.7001</t>
+          <t>0.7143</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.79 ± 0.33</t>
+          <t>9.29 ± 0.49</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2.13 ± 0.32</t>
+          <t>9.04 ± 0.31</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2.25 ± 0.42</t>
+          <t>9.53 ± 0.44</t>
         </is>
       </c>
     </row>
@@ -666,42 +666,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Water DO Bottom (mg/L)</t>
+          <t>LOI (%)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.73</v>
+        <v>1.84</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>140.38</v>
+        <v>118.69</v>
       </c>
       <c r="F6" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G6" t="n">
-        <v>0.14</v>
+        <v>0.33</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.8670</t>
+          <t>0.7184</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>9.07 ± 0.46</t>
+          <t>1.77 ± 0.33</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>9.12 ± 0.28</t>
+          <t>2.00 ± 0.38</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>9.34 ± 0.39</t>
+          <t>2.27 ± 0.54</t>
         </is>
       </c>
     </row>
@@ -739,10 +739,10 @@
         <v>15</v>
       </c>
       <c r="J8" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="K8" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">

--- a/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/anova_env.xlsx
+++ b/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/anova_env.xlsx
@@ -490,38 +490,38 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>219.09</v>
+        <v>284.06</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>439.71</v>
+        <v>423.45</v>
       </c>
       <c r="F2" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G2" t="n">
-        <v>10.71</v>
+        <v>16.77</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.0002***</t>
+          <t>0.0000***</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7.78 ± 1.01</t>
+          <t>8.21 ± 0.98</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2.68 ± 0.57</t>
+          <t>2.61 ± 0.45</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>3.82 ± 0.85</t>
+          <t>3.51 ± 0.73</t>
         </is>
       </c>
     </row>
@@ -535,38 +535,38 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2.62</v>
+        <v>3.12</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>18.95</v>
+        <v>20.9</v>
       </c>
       <c r="F3" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G3" t="n">
-        <v>2.98</v>
+        <v>3.74</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0616.</t>
+          <t>0.0308*</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.85 ± 0.20</t>
+          <t>0.83 ± 0.21</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1.34 ± 0.11</t>
+          <t>1.27 ± 0.10</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.37 ± 0.20</t>
+          <t>1.45 ± 0.17</t>
         </is>
       </c>
     </row>
@@ -580,38 +580,38 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8.16</v>
+        <v>12.67</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>261.71</v>
+        <v>265.4</v>
       </c>
       <c r="F4" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G4" t="n">
-        <v>0.67</v>
+        <v>1.19</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.5167</t>
+          <t>0.3117</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>18.92 ± 0.63</t>
+          <t>18.80 ± 0.67</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>19.55 ± 0.45</t>
+          <t>19.72 ± 0.36</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>19.96 ± 0.79</t>
+          <t>20.04 ± 0.65</t>
         </is>
       </c>
     </row>
@@ -621,42 +621,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Water DO Bottom (mg/L)</t>
+          <t>LOI (%)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>115.55</v>
+        <v>139.21</v>
       </c>
       <c r="F5" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G5" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.7143</t>
+          <t>0.7236</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>9.29 ± 0.49</t>
+          <t>1.79 ± 0.36</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>9.04 ± 0.31</t>
+          <t>2.16 ± 0.36</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>9.53 ± 0.44</t>
+          <t>2.25 ± 0.45</t>
         </is>
       </c>
     </row>
@@ -666,42 +666,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LOI (%)</t>
+          <t>Water DO Bottom (mg/L)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.84</v>
+        <v>0.38</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>118.69</v>
+        <v>132.86</v>
       </c>
       <c r="F6" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>0.33</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.7184</t>
+          <t>0.9318</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.77 ± 0.33</t>
+          <t>9.12 ± 0.49</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2.00 ± 0.38</t>
+          <t>9.14 ± 0.30</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2.27 ± 0.54</t>
+          <t>9.31 ± 0.41</t>
         </is>
       </c>
     </row>
@@ -736,13 +736,13 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J8" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K8" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">

--- a/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/anova_env.xlsx
+++ b/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/anova_env.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,11 +474,6 @@
           <t>Cluster C2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Cluster C3</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -490,38 +485,33 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>284.06</v>
+        <v>147.14</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>423.45</v>
+        <v>403</v>
       </c>
       <c r="F2" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G2" t="n">
-        <v>16.77</v>
+        <v>13.87</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.0000***</t>
+          <t>0.0006***</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.21 ± 0.98</t>
+          <t>7.58 ± 1.08</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2.61 ± 0.45</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>3.51 ± 0.73</t>
+          <t>3.49 ± 0.56</t>
         </is>
       </c>
     </row>
@@ -535,38 +525,33 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3.12</v>
+        <v>1.96</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>20.9</v>
+        <v>18.38</v>
       </c>
       <c r="F3" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G3" t="n">
-        <v>3.74</v>
+        <v>4.06</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0308*</t>
+          <t>0.0511.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.83 ± 0.21</t>
+          <t>0.84 ± 0.23</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1.27 ± 0.10</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>1.45 ± 0.17</t>
+          <t>1.32 ± 0.12</t>
         </is>
       </c>
     </row>
@@ -580,38 +565,33 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12.67</v>
+        <v>3.59</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>265.4</v>
+        <v>209</v>
       </c>
       <c r="F4" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G4" t="n">
-        <v>1.19</v>
+        <v>0.65</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.3117</t>
+          <t>0.4239</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>18.80 ± 0.67</t>
+          <t>19.25 ± 0.62</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>19.72 ± 0.36</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>20.04 ± 0.65</t>
+          <t>19.89 ± 0.46</t>
         </is>
       </c>
     </row>
@@ -625,38 +605,33 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.81</v>
+        <v>0.54</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>139.21</v>
+        <v>89.97</v>
       </c>
       <c r="F5" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G5" t="n">
-        <v>0.33</v>
+        <v>0.23</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.7236</t>
+          <t>0.6346</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.79 ± 0.36</t>
+          <t>1.73 ± 0.38</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2.16 ± 0.36</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2.25 ± 0.45</t>
+          <t>1.98 ± 0.31</t>
         </is>
       </c>
     </row>
@@ -670,38 +645,33 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.38</v>
+        <v>0.01</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>132.86</v>
+        <v>65.37</v>
       </c>
       <c r="F6" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.9318</t>
+          <t>0.9497</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>9.12 ± 0.49</t>
+          <t>9.10 ± 0.39</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>9.14 ± 0.30</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>9.31 ± 0.41</t>
+          <t>9.07 ± 0.24</t>
         </is>
       </c>
     </row>
@@ -718,7 +688,6 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -736,13 +705,10 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J8" t="n">
-        <v>21</v>
-      </c>
-      <c r="K8" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
@@ -758,7 +724,6 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -777,7 +742,6 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
